--- a/hall/resources/sample/SeasonGem.xlsx
+++ b/hall/resources/sample/SeasonGem.xlsx
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -82,16 +82,44 @@
         </r>
       </text>
     </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+模式id&amp;进去此模式的权重值增加值</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="127">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>游戏ID</t>
+  </si>
+  <si>
+    <t>游戏名称</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -101,33 +129,51 @@
     <t>品质</t>
   </si>
   <si>
+    <t>道具ID</t>
+  </si>
+  <si>
     <t>流派名称</t>
   </si>
   <si>
-    <t>宝石名称</t>
+    <t>宝石名称多语言</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>宝石描述</t>
-  </si>
-  <si>
-    <t>提升效率（百分比）</t>
-  </si>
-  <si>
-    <t>客户端资源</t>
+    <t>宝石描述多语言</t>
+  </si>
+  <si>
+    <t>金额解锁</t>
+  </si>
+  <si>
+    <t>中奖概率提升</t>
+  </si>
+  <si>
+    <t>进入特殊模式概率提升</t>
+  </si>
+  <si>
+    <t>特殊模式中奖概率提升</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
+    <t>list&lt;long&gt;{_}</t>
+  </si>
+  <si>
+    <t>map&lt;int{,}map&lt;int{_}int&gt;{|}&gt;{;}</t>
+  </si>
+  <si>
+    <t>map&lt;int{,}int&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>gameID</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -137,16 +183,28 @@
     <t>Rarity</t>
   </si>
   <si>
+    <t>itemId</t>
+  </si>
+  <si>
     <t>GemName</t>
   </si>
   <si>
     <t>GemDesc</t>
   </si>
   <si>
-    <t>buff</t>
-  </si>
-  <si>
-    <t>icon</t>
+    <t>bet</t>
+  </si>
+  <si>
+    <t>winRate</t>
+  </si>
+  <si>
+    <t>specialMode</t>
+  </si>
+  <si>
+    <t>specialModeProbUp</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
   </si>
   <si>
     <t>基础命中</t>
@@ -158,61 +216,91 @@
     <t>普通模式Spin基础中奖概率+3%</t>
   </si>
   <si>
+    <t>1,0_-6000</t>
+  </si>
+  <si>
     <t>基础命中.绿</t>
   </si>
   <si>
     <t>普通模式Spin基础中奖概率+6%</t>
   </si>
   <si>
+    <t>1,0_-12000</t>
+  </si>
+  <si>
     <t>基础命中.蓝</t>
   </si>
   <si>
     <t>普通模式Spin基础中奖概率+10%</t>
   </si>
   <si>
+    <t>1,0_-18000</t>
+  </si>
+  <si>
     <t>基础命中.紫</t>
   </si>
   <si>
     <t>普通模式Spin基础中奖概率+15%</t>
   </si>
   <si>
+    <t>1,0_-24000</t>
+  </si>
+  <si>
     <t>基础命中.橙</t>
   </si>
   <si>
     <t>普通模式Spin基础中奖概率+20%</t>
   </si>
   <si>
+    <t>1,0_-29000</t>
+  </si>
+  <si>
     <t>免费命中</t>
   </si>
   <si>
     <t>免费命中.白</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内中奖概率+3%</t>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+1%</t>
+  </si>
+  <si>
+    <t>2,24_1700</t>
   </si>
   <si>
     <t>免费命中.绿</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内中奖概率+6%</t>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+2%</t>
+  </si>
+  <si>
+    <t>2,24_3800</t>
   </si>
   <si>
     <t>免费命中.蓝</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内中奖概率+10%</t>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+3%</t>
+  </si>
+  <si>
+    <t>2,24_5800</t>
   </si>
   <si>
     <t>免费命中.紫</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内中奖概率+15%</t>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+4%</t>
+  </si>
+  <si>
+    <t>2,24_8200</t>
   </si>
   <si>
     <t>免费命中.橙</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内中奖概率+20%</t>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+5%</t>
+  </si>
+  <si>
+    <t>2,24_8500</t>
   </si>
   <si>
     <t>大奖冲刺</t>
@@ -221,31 +309,46 @@
     <t>大奖冲刺.白</t>
   </si>
   <si>
-    <t>50-100倍区间的触发概率+2%</t>
+    <t>20-50倍区间的触发概率+2%</t>
+  </si>
+  <si>
+    <t>1,18_100</t>
   </si>
   <si>
     <t>大奖冲刺.绿</t>
   </si>
   <si>
-    <t>50-100倍区间的触发概率+4%</t>
+    <t>20-50倍区间的触发概率+4%</t>
+  </si>
+  <si>
+    <t>1,18_200</t>
   </si>
   <si>
     <t>大奖冲刺.蓝</t>
   </si>
   <si>
-    <t>50-100倍区间的触发概率+6%</t>
+    <t>20-50倍区间的触发概率+6%</t>
+  </si>
+  <si>
+    <t>1,18_300</t>
   </si>
   <si>
     <t>大奖冲刺.紫</t>
   </si>
   <si>
-    <t>50-100倍区间的触发概率+8%</t>
+    <t>20-50倍区间的触发概率+8%</t>
+  </si>
+  <si>
+    <t>1,18_400</t>
   </si>
   <si>
     <t>大奖冲刺.橙</t>
   </si>
   <si>
-    <t>50-100倍区间的触发概率+10%</t>
+    <t>20-50倍区间的触发概率+10%</t>
+  </si>
+  <si>
+    <t>1,18_500</t>
   </si>
   <si>
     <t>基础收益</t>
@@ -254,31 +357,46 @@
     <t>基础收益.白</t>
   </si>
   <si>
-    <t>10-20倍区间的中奖概率+2%</t>
+    <t>5-10倍区间的中奖概率+2%</t>
+  </si>
+  <si>
+    <t>1,8_500</t>
   </si>
   <si>
     <t>基础收益.绿</t>
   </si>
   <si>
-    <t>10-20倍区间的中奖概率+4%</t>
+    <t>5-10倍区间的中奖概率+4%</t>
+  </si>
+  <si>
+    <t>1,8_1000</t>
   </si>
   <si>
     <t>基础收益.蓝</t>
   </si>
   <si>
-    <t>10-20倍区间的中奖概率+6%</t>
+    <t>5-10倍区间的中奖概率+6%</t>
+  </si>
+  <si>
+    <t>1,8_1500</t>
   </si>
   <si>
     <t>基础收益.紫</t>
   </si>
   <si>
-    <t>10-20倍区间的中奖概率+8%</t>
+    <t>5-10倍区间的中奖概率+8%</t>
+  </si>
+  <si>
+    <t>1,8_2000</t>
   </si>
   <si>
     <t>基础收益.橙</t>
   </si>
   <si>
-    <t>10-20倍区间的中奖概率+10%</t>
+    <t>5-10倍区间的中奖概率+10%</t>
+  </si>
+  <si>
+    <t>1,8_2500</t>
   </si>
   <si>
     <t>免费模式</t>
@@ -290,30 +408,45 @@
     <t>进入免费旋转模式的概率+2%</t>
   </si>
   <si>
+    <t>2,2</t>
+  </si>
+  <si>
     <t>免费模式.绿</t>
   </si>
   <si>
     <t>进入免费旋转模式的概率+4%</t>
   </si>
   <si>
+    <t>2,4</t>
+  </si>
+  <si>
     <t>免费模式.蓝</t>
   </si>
   <si>
     <t>进入免费旋转模式的概率+6%</t>
   </si>
   <si>
+    <t>2,6</t>
+  </si>
+  <si>
     <t>免费模式.紫</t>
   </si>
   <si>
     <t>进入免费旋转模式的概率+8%</t>
   </si>
   <si>
+    <t>2,8</t>
+  </si>
+  <si>
     <t>免费模式.橙</t>
   </si>
   <si>
     <t>进入免费旋转模式的概率+10%</t>
   </si>
   <si>
+    <t>2,10</t>
+  </si>
+  <si>
     <t>下注提升</t>
   </si>
   <si>
@@ -329,22 +462,34 @@
     <t>下注的金额提升到400%</t>
   </si>
   <si>
+    <t>200_400</t>
+  </si>
+  <si>
     <t>下注提升.蓝</t>
   </si>
   <si>
     <t>下注的金额提升到600%</t>
   </si>
   <si>
+    <t>200_400_600</t>
+  </si>
+  <si>
     <t>下注提升.紫</t>
   </si>
   <si>
     <t>下注的金额提升到800%</t>
   </si>
   <si>
+    <t>200_400_600_800</t>
+  </si>
+  <si>
     <t>下注提升.橙</t>
   </si>
   <si>
     <t>下注的金额提升到1000%</t>
+  </si>
+  <si>
+    <t>200_400_600_800_1000</t>
   </si>
 </sst>
 </file>
@@ -357,7 +502,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,11 +525,6 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -544,7 +684,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,25 +693,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="2" tint="-0.1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,27 +884,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9DEE7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9DEE7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9DEE7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9DEE7"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -903,137 +1010,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1049,29 +1156,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1598,22 +1687,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="15.125" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="13.25" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="10" width="24.25" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="2" max="2" width="10.375" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="6.5" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="15.25" customWidth="1"/>
+    <col min="10" max="10" width="12.25" customWidth="1"/>
+    <col min="11" max="11" width="14.75" customWidth="1"/>
+    <col min="12" max="12" width="34.25" customWidth="1"/>
+    <col min="13" max="13" width="24.25" customWidth="1"/>
+    <col min="14" max="14" width="16.625" customWidth="1"/>
+    <col min="15" max="15" width="21.125" customWidth="1"/>
+    <col min="16" max="16" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,75 +1732,116 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:11">
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:11">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:16">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1718,1416 +1853,1765 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="4">
-        <f t="shared" ref="A5:A34" si="0">B5*10000+C5*100+D5</f>
-        <v>10101</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:16">
+      <c r="A5" s="1">
+        <v>100101</v>
+      </c>
+      <c r="B5" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="4">
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+      <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="G5" s="1">
         <v>1131001</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1131001</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="1">
         <v>2131001</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="L5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:16">
+      <c r="A6" s="1">
+        <v>100102</v>
+      </c>
+      <c r="B6" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1131101</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1131101</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2131101</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:16">
+      <c r="A7" s="1">
+        <v>100103</v>
+      </c>
+      <c r="B7" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
         <v>3</v>
       </c>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="4">
-        <f t="shared" si="0"/>
-        <v>10102</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="G7" s="1">
+        <v>1131201</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1131201</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2131201</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:16">
+      <c r="A8" s="1">
+        <v>100104</v>
+      </c>
+      <c r="B8" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="4">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1131101</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2131101</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="4">
-        <v>6</v>
-      </c>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="1">
-        <f t="shared" si="0"/>
-        <v>10103</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="F8" s="1">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1131301</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1131301</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2131301</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:16">
+      <c r="A9" s="1">
+        <v>100105</v>
+      </c>
+      <c r="B9" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="4">
+      <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1131201</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2131201</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="1">
-        <v>10</v>
-      </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="1">
-        <f t="shared" si="0"/>
-        <v>10104</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>4</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1131301</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="1">
-        <v>2131301</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="1">
-        <v>15</v>
-      </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="1">
-        <f t="shared" si="0"/>
-        <v>10105</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="F9" s="1">
         <v>5</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>1131401</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1131401</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="1">
         <v>2131401</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="1">
-        <v>20</v>
-      </c>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>10201</v>
-      </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2</v>
+      <c r="L9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:16">
+      <c r="A10" s="1">
+        <v>100106</v>
+      </c>
+      <c r="B10" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1131002</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1131002</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="4">
+        <v>2131002</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="P10" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:16">
+      <c r="A11" s="1">
+        <v>100107</v>
+      </c>
+      <c r="B11" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="4">
-        <v>1131002</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="4">
-        <v>2131002</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="4">
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1131102</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1131102</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="4">
+        <v>2131102</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:16">
+      <c r="A12" s="1">
+        <v>100108</v>
+      </c>
+      <c r="B12" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
         <v>3</v>
       </c>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>10202</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="G12" s="4">
+        <v>1131202</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1131202</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="4">
+        <v>2131202</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="P12" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:16">
+      <c r="A13" s="1">
+        <v>100109</v>
+      </c>
+      <c r="B13" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="C11" s="4">
+      <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="D11" s="4">
+      <c r="F13" s="4">
+        <v>4</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1131302</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1131302</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="4">
+        <v>2131302</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="P13" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:16">
+      <c r="A14" s="1">
+        <v>100110</v>
+      </c>
+      <c r="B14" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
         <v>2</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F14" s="4">
+        <v>5</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1131402</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1131402</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="4">
+        <v>2131402</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="P14" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:16">
+      <c r="A15" s="1">
+        <v>100201</v>
+      </c>
+      <c r="B15" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="4">
-        <v>1131102</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="4">
-        <v>2131102</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="4">
-        <v>6</v>
-      </c>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:11">
-      <c r="A12" s="1">
-        <f t="shared" si="0"/>
-        <v>10203</v>
-      </c>
-      <c r="B12" s="1">
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="4">
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1131004</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1131003</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2131003</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:16">
+      <c r="A16" s="1">
+        <v>100202</v>
+      </c>
+      <c r="B16" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1131104</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1131103</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2131103</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:15">
+      <c r="A17" s="1">
+        <v>100203</v>
+      </c>
+      <c r="B17" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
         <v>3</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="G17" s="1">
+        <v>1131204</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1131203</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" s="1">
+        <v>2131203</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:15">
+      <c r="A18" s="1">
+        <v>100204</v>
+      </c>
+      <c r="B18" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="4">
-        <v>1131202</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="4">
-        <v>2131202</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="1">
-        <v>10</v>
-      </c>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
-      <c r="A13" s="1">
-        <f t="shared" si="0"/>
-        <v>10204</v>
-      </c>
-      <c r="B13" s="1">
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="4">
+      <c r="F18" s="1">
+        <v>4</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1131304</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1131303</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" s="1">
+        <v>2131303</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:15">
+      <c r="A19" s="1">
+        <v>100205</v>
+      </c>
+      <c r="B19" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1">
         <v>2</v>
       </c>
-      <c r="D13" s="1">
-        <v>4</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1131404</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1131403</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2131403</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:15">
+      <c r="A20" s="1">
+        <v>100206</v>
+      </c>
+      <c r="B20" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="4">
-        <v>1131302</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="4">
-        <v>2131302</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="1">
-        <v>15</v>
-      </c>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>10205</v>
-      </c>
-      <c r="B14" s="1">
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4">
         <v>1</v>
       </c>
-      <c r="C14" s="4">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1">
-        <v>5</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="G20" s="4">
+        <v>1131003</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1131004</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="4">
+        <v>2131004</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:15">
+      <c r="A21" s="1">
+        <v>100207</v>
+      </c>
+      <c r="B21" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1131402</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="4">
-        <v>2131402</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" s="1">
-        <v>20</v>
-      </c>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:11">
-      <c r="A15" s="4">
-        <f t="shared" si="0"/>
-        <v>20101</v>
-      </c>
-      <c r="B15" s="4">
-        <v>2</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1131003</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="4">
-        <v>2131003</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" s="4">
-        <v>2</v>
-      </c>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:11">
-      <c r="A16" s="4">
-        <f t="shared" si="0"/>
-        <v>20102</v>
-      </c>
-      <c r="B16" s="4">
-        <v>2</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1131103</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="4">
-        <v>2131103</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="4">
-        <v>4</v>
-      </c>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>20103</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1">
-        <v>3</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1131203</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="4">
-        <v>2131203</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" s="1">
-        <v>6</v>
-      </c>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>20104</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>4</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1131303</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="4">
-        <v>2131303</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="1">
-        <v>8</v>
-      </c>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:11">
-      <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>20105</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1">
-        <v>5</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1131403</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="4">
-        <v>2131403</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="1">
-        <v>10</v>
-      </c>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="4">
-        <f t="shared" si="0"/>
-        <v>20201</v>
-      </c>
-      <c r="B20" s="4">
-        <v>2</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="4">
-        <v>1131004</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H20" s="4">
-        <v>2131004</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="4">
-        <v>2</v>
-      </c>
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:11">
-      <c r="A21" s="4">
-        <f t="shared" si="0"/>
-        <v>20202</v>
-      </c>
-      <c r="B21" s="4">
-        <v>2</v>
-      </c>
-      <c r="C21" s="4">
-        <v>2</v>
       </c>
       <c r="D21" s="4">
         <v>2</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>53</v>
+      <c r="E21" s="4">
+        <v>2</v>
       </c>
       <c r="F21" s="4">
+        <v>2</v>
+      </c>
+      <c r="G21" s="4">
+        <v>1131103</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="4">
         <v>1131104</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H21" s="4">
+      <c r="J21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" s="4">
         <v>2131104</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J21" s="4">
+      <c r="L21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:15">
+      <c r="A22" s="1">
+        <v>100208</v>
+      </c>
+      <c r="B22" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>3</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1131203</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1131204</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K22" s="4">
+        <v>2131204</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:15">
+      <c r="A23" s="1">
+        <v>100209</v>
+      </c>
+      <c r="B23" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4">
         <v>4</v>
       </c>
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="1">
-        <f t="shared" si="0"/>
-        <v>20203</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="G23" s="4">
+        <v>1131303</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1131304</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K23" s="4">
+        <v>2131304</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:15">
+      <c r="A24" s="1">
+        <v>100210</v>
+      </c>
+      <c r="B24" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="4">
         <v>2</v>
       </c>
-      <c r="C22" s="4">
+      <c r="E24" s="4">
         <v>2</v>
       </c>
-      <c r="D22" s="1">
+      <c r="F24" s="4">
+        <v>5</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1131403</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1131404</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K24" s="4">
+        <v>2131404</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:15">
+      <c r="A25" s="1">
+        <v>100301</v>
+      </c>
+      <c r="B25" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="1">
         <v>3</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1131204</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" s="4">
-        <v>2131204</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J22" s="1">
-        <v>6</v>
-      </c>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="1">
-        <f t="shared" si="0"/>
-        <v>20204</v>
-      </c>
-      <c r="B23" s="1">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1131005</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1131005</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K25" s="1">
+        <v>2131005</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:15">
+      <c r="A26" s="1">
+        <v>100302</v>
+      </c>
+      <c r="B26" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
         <v>2</v>
       </c>
-      <c r="C23" s="4">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1">
-        <v>4</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" s="4">
-        <v>1131304</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" s="4">
-        <v>2131304</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="J23" s="1">
-        <v>8</v>
-      </c>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
-      <c r="A24" s="1">
-        <f t="shared" si="0"/>
-        <v>20205</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="4">
-        <v>2</v>
-      </c>
-      <c r="D24" s="1">
-        <v>5</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="4">
-        <v>1131404</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="4">
-        <v>2131404</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="J24" s="1">
-        <v>10</v>
-      </c>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:11">
-      <c r="A25" s="4">
-        <f t="shared" si="0"/>
-        <v>30101</v>
-      </c>
-      <c r="B25" s="4">
-        <v>3</v>
-      </c>
-      <c r="C25" s="4">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" s="4">
-        <v>1131005</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" s="4">
-        <v>2131005</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J25" s="4">
-        <v>2</v>
-      </c>
-      <c r="K25" s="4"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:11">
-      <c r="A26" s="4">
-        <f t="shared" si="0"/>
-        <v>30102</v>
-      </c>
-      <c r="B26" s="4">
-        <v>3</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-      <c r="D26" s="4">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="4">
+      <c r="G26" s="1">
         <v>1131105</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="4">
+      <c r="H26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1131105</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K26" s="1">
         <v>2131105</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J26" s="4">
-        <v>4</v>
-      </c>
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:11">
+      <c r="L26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:15">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
-        <v>30103</v>
+        <v>100303</v>
       </c>
       <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1</v>
+        <v>103800</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="4">
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
         <v>1131205</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="H27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1131205</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K27" s="1">
         <v>2131205</v>
       </c>
-      <c r="I27" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="J27" s="1">
-        <v>6</v>
-      </c>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:11">
+      <c r="L27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:15">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
-        <v>30104</v>
+        <v>100304</v>
       </c>
       <c r="B28" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="1">
         <v>3</v>
       </c>
-      <c r="C28" s="4">
+      <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="D28" s="1">
+      <c r="F28" s="1">
         <v>4</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="4">
+      <c r="G28" s="1">
         <v>1131305</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="4">
+      <c r="H28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1131305</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K28" s="1">
         <v>2131305</v>
       </c>
-      <c r="I28" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J28" s="1">
-        <v>8</v>
-      </c>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:11">
+      <c r="L28" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:15">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
-        <v>30105</v>
+        <v>100305</v>
       </c>
       <c r="B29" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="1">
         <v>3</v>
       </c>
-      <c r="C29" s="4">
+      <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="D29" s="1">
+      <c r="F29" s="1">
         <v>5</v>
       </c>
-      <c r="E29" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F29" s="4">
+      <c r="G29" s="1">
         <v>1131405</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="4">
+      <c r="H29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1131405</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K29" s="1">
         <v>2131405</v>
       </c>
-      <c r="I29" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" s="1">
-        <v>10</v>
-      </c>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:11">
-      <c r="A30" s="4">
-        <f t="shared" si="0"/>
-        <v>30201</v>
-      </c>
-      <c r="B30" s="4">
+      <c r="L29" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:15">
+      <c r="A30" s="1">
+        <v>100306</v>
+      </c>
+      <c r="B30" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="4">
         <v>3</v>
       </c>
-      <c r="C30" s="4">
+      <c r="E30" s="4">
         <v>2</v>
       </c>
-      <c r="D30" s="4">
+      <c r="F30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="4">
+      <c r="G30" s="4">
         <v>1131006</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H30" s="4">
+      <c r="H30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1131006</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K30" s="4">
         <v>2131006</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30" s="4">
+      <c r="L30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M30" s="2">
         <v>200</v>
       </c>
-      <c r="K30" s="4"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:11">
-      <c r="A31" s="4">
-        <f t="shared" si="0"/>
-        <v>30202</v>
-      </c>
-      <c r="B31" s="4">
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:15">
+      <c r="A31" s="1">
+        <v>100307</v>
+      </c>
+      <c r="B31" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="4">
         <v>3</v>
       </c>
-      <c r="C31" s="4">
+      <c r="E31" s="4">
         <v>2</v>
       </c>
-      <c r="D31" s="4">
+      <c r="F31" s="4">
         <v>2</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="G31" s="4">
         <v>1131106</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" s="4">
+      <c r="H31" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1131106</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K31" s="4">
         <v>2131106</v>
       </c>
-      <c r="I31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J31" s="4">
-        <v>400</v>
-      </c>
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:11">
+      <c r="L31" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:15">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
-        <v>30203</v>
+        <v>100308</v>
       </c>
       <c r="B32" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="4">
         <v>3</v>
       </c>
-      <c r="C32" s="4">
+      <c r="E32" s="4">
         <v>2</v>
       </c>
-      <c r="D32" s="1">
+      <c r="F32" s="4">
         <v>3</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="4">
+      <c r="G32" s="4">
         <v>1131206</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H32" s="4">
+      <c r="H32" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1131206</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32" s="4">
         <v>2131206</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32" s="1">
-        <v>600</v>
-      </c>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:11">
+      <c r="L32" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:14">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
-        <v>30204</v>
+        <v>100309</v>
       </c>
       <c r="B33" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="4">
         <v>3</v>
       </c>
-      <c r="C33" s="4">
+      <c r="E33" s="4">
         <v>2</v>
       </c>
-      <c r="D33" s="1">
+      <c r="F33" s="4">
         <v>4</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="4">
+      <c r="G33" s="4">
         <v>1131306</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" s="4">
+      <c r="H33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I33" s="4">
+        <v>1131306</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" s="4">
         <v>2131306</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J33" s="1">
-        <v>800</v>
-      </c>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:11">
+      <c r="L33" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:14">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
-        <v>30205</v>
+        <v>100310</v>
       </c>
       <c r="B34" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="4">
         <v>3</v>
       </c>
-      <c r="C34" s="4">
+      <c r="E34" s="4">
         <v>2</v>
       </c>
-      <c r="D34" s="1">
+      <c r="F34" s="4">
         <v>5</v>
       </c>
-      <c r="E34" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="4">
+      <c r="G34" s="4">
         <v>1131406</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="4">
+      <c r="H34" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1131406</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K34" s="4">
         <v>2131406</v>
       </c>
-      <c r="I34" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:11">
+      <c r="L34" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:14">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="12"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="10"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:11">
+      <c r="L35" s="6"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:14">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="12"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="10"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:11">
+      <c r="L36" s="6"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:14">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="12"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="10"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:11">
+      <c r="L37" s="6"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:14">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="12"/>
+      <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="10"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:11">
+      <c r="L38" s="6"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:14">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="12"/>
+      <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="10"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:11">
+      <c r="L39" s="6"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:14">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="12"/>
+      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="10"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:11">
+      <c r="L40" s="6"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:14">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="12"/>
+      <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="10"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:11">
+      <c r="L41" s="6"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:14">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="12"/>
+      <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="10"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:11">
+      <c r="L42" s="6"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:14">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="12"/>
+      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="10"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:11">
+      <c r="L43" s="6"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:14">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="12"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="10"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:11">
+      <c r="L44" s="6"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:14">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="12"/>
+      <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="10"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:11">
+      <c r="L45" s="6"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:14">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="12"/>
+      <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="10"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:11">
+      <c r="L46" s="6"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:14">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="12"/>
+      <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="10"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:11">
+      <c r="L47" s="6"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:14">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="12"/>
+      <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="10"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:11">
+      <c r="L48" s="6"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:14">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="12"/>
+      <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="10"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:11">
+      <c r="L49" s="6"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:14">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="12"/>
+      <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="10"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:11">
+      <c r="L50" s="6"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:14">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="12"/>
+      <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="10"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:11">
+      <c r="L51" s="6"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:14">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="12"/>
+      <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="10"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:11">
+      <c r="L52" s="6"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:14">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="12"/>
+      <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="10"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:11">
+      <c r="L53" s="6"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:14">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="12"/>
+      <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="10"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:11">
+      <c r="L54" s="6"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:14">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="12"/>
+      <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="10"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:11">
+      <c r="L55" s="6"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:14">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="12"/>
+      <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="10"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:11">
+      <c r="L56" s="6"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:14">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="12"/>
+      <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="10"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:11">
+      <c r="L57" s="6"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:14">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="12"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="10"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:11">
+      <c r="L58" s="6"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:14">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="12"/>
+      <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="10"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:11">
+      <c r="L59" s="6"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:14">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="12"/>
+      <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="10"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:11">
+      <c r="L60" s="6"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:14">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="12"/>
+      <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="10"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:11">
+      <c r="L61" s="6"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:14">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
-      <c r="E62" s="12"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="10"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:11">
+      <c r="L62" s="6"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:14">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="12"/>
+      <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="10"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:11">
+      <c r="L63" s="6"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:14">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
-      <c r="E64" s="12"/>
+      <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="10"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/SeasonGem.xlsx
+++ b/hall/resources/sample/SeasonGem.xlsx
@@ -56,33 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1-白色
-2-绿色
-3-蓝色
-4-紫色
-5-橙色</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -109,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
   <si>
     <t>ID</t>
   </si>
@@ -126,24 +100,15 @@
     <t>流派</t>
   </si>
   <si>
-    <t>品质</t>
+    <t>流派名称</t>
   </si>
   <si>
     <t>道具ID</t>
   </si>
   <si>
-    <t>流派名称</t>
-  </si>
-  <si>
-    <t>宝石名称多语言</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
-    <t>宝石描述多语言</t>
-  </si>
-  <si>
     <t>金额解锁</t>
   </si>
   <si>
@@ -180,18 +145,9 @@
     <t>Genre</t>
   </si>
   <si>
-    <t>Rarity</t>
-  </si>
-  <si>
     <t>itemId</t>
   </si>
   <si>
-    <t>GemName</t>
-  </si>
-  <si>
-    <t>GemDesc</t>
-  </si>
-  <si>
     <t>bet</t>
   </si>
   <si>
@@ -213,45 +169,30 @@
     <t>基础命中.白</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+3%</t>
-  </si>
-  <si>
     <t>1,0_-6000</t>
   </si>
   <si>
     <t>基础命中.绿</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+6%</t>
-  </si>
-  <si>
     <t>1,0_-12000</t>
   </si>
   <si>
     <t>基础命中.蓝</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+10%</t>
-  </si>
-  <si>
     <t>1,0_-18000</t>
   </si>
   <si>
     <t>基础命中.紫</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+15%</t>
-  </si>
-  <si>
     <t>1,0_-24000</t>
   </si>
   <si>
     <t>基础命中.橙</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+20%</t>
-  </si>
-  <si>
     <t>1,0_-29000</t>
   </si>
   <si>
@@ -261,45 +202,30 @@
     <t>免费命中.白</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+1%</t>
-  </si>
-  <si>
     <t>2,24_1700</t>
   </si>
   <si>
     <t>免费命中.绿</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+2%</t>
-  </si>
-  <si>
     <t>2,24_3800</t>
   </si>
   <si>
     <t>免费命中.蓝</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+3%</t>
-  </si>
-  <si>
     <t>2,24_5800</t>
   </si>
   <si>
     <t>免费命中.紫</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+4%</t>
-  </si>
-  <si>
     <t>2,24_8200</t>
   </si>
   <si>
     <t>免费命中.橙</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+5%</t>
-  </si>
-  <si>
     <t>2,24_8500</t>
   </si>
   <si>
@@ -309,45 +235,30 @@
     <t>大奖冲刺.白</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+2%</t>
-  </si>
-  <si>
     <t>1,18_100</t>
   </si>
   <si>
     <t>大奖冲刺.绿</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+4%</t>
-  </si>
-  <si>
     <t>1,18_200</t>
   </si>
   <si>
     <t>大奖冲刺.蓝</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+6%</t>
-  </si>
-  <si>
     <t>1,18_300</t>
   </si>
   <si>
     <t>大奖冲刺.紫</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+8%</t>
-  </si>
-  <si>
     <t>1,18_400</t>
   </si>
   <si>
     <t>大奖冲刺.橙</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+10%</t>
-  </si>
-  <si>
     <t>1,18_500</t>
   </si>
   <si>
@@ -357,45 +268,30 @@
     <t>基础收益.白</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+2%</t>
-  </si>
-  <si>
     <t>1,8_500</t>
   </si>
   <si>
     <t>基础收益.绿</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+4%</t>
-  </si>
-  <si>
     <t>1,8_1000</t>
   </si>
   <si>
     <t>基础收益.蓝</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+6%</t>
-  </si>
-  <si>
     <t>1,8_1500</t>
   </si>
   <si>
     <t>基础收益.紫</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+8%</t>
-  </si>
-  <si>
     <t>1,8_2000</t>
   </si>
   <si>
     <t>基础收益.橙</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+10%</t>
-  </si>
-  <si>
     <t>1,8_2500</t>
   </si>
   <si>
@@ -405,45 +301,30 @@
     <t>免费模式.白</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+2%</t>
-  </si>
-  <si>
     <t>2,2</t>
   </si>
   <si>
     <t>免费模式.绿</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+4%</t>
-  </si>
-  <si>
     <t>2,4</t>
   </si>
   <si>
     <t>免费模式.蓝</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+6%</t>
-  </si>
-  <si>
     <t>2,6</t>
   </si>
   <si>
     <t>免费模式.紫</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+8%</t>
-  </si>
-  <si>
     <t>2,8</t>
   </si>
   <si>
     <t>免费模式.橙</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+10%</t>
-  </si>
-  <si>
     <t>2,10</t>
   </si>
   <si>
@@ -453,40 +334,25 @@
     <t>下注提升.白</t>
   </si>
   <si>
-    <t>下注的金额提升到200%</t>
-  </si>
-  <si>
     <t>下注提升.绿</t>
   </si>
   <si>
-    <t>下注的金额提升到400%</t>
-  </si>
-  <si>
     <t>200_400</t>
   </si>
   <si>
     <t>下注提升.蓝</t>
   </si>
   <si>
-    <t>下注的金额提升到600%</t>
-  </si>
-  <si>
     <t>200_400_600</t>
   </si>
   <si>
     <t>下注提升.紫</t>
   </si>
   <si>
-    <t>下注的金额提升到800%</t>
-  </si>
-  <si>
     <t>200_400_600_800</t>
   </si>
   <si>
     <t>下注提升.橙</t>
-  </si>
-  <si>
-    <t>下注的金额提升到1000%</t>
   </si>
   <si>
     <t>200_400_600_800_1000</t>
@@ -1140,27 +1006,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1687,27 +1550,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
     <col min="3" max="3" width="10.625" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="6.5" customWidth="1"/>
-    <col min="6" max="6" width="8.5" customWidth="1"/>
-    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="6" max="6" width="12.375" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="12.875" customWidth="1"/>
-    <col min="9" max="9" width="15.25" customWidth="1"/>
-    <col min="10" max="10" width="12.25" customWidth="1"/>
-    <col min="11" max="11" width="14.75" customWidth="1"/>
-    <col min="12" max="12" width="34.25" customWidth="1"/>
-    <col min="13" max="13" width="24.25" customWidth="1"/>
-    <col min="14" max="14" width="16.625" customWidth="1"/>
-    <col min="15" max="15" width="21.125" customWidth="1"/>
-    <col min="16" max="16" width="19.625" customWidth="1"/>
+    <col min="9" max="9" width="24.25" customWidth="1"/>
+    <col min="10" max="10" width="16.625" customWidth="1"/>
+    <col min="11" max="11" width="21.125" customWidth="1"/>
+    <col min="12" max="12" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:16">
+    <row r="1" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1741,107 +1600,75 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:12">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:16">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:12">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:16">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:16">
+        <v>23</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1853,12 +1680,8 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:16">
+    </row>
+    <row r="5" customHeight="1" spans="1:12">
       <c r="A5" s="1">
         <v>100101</v>
       </c>
@@ -1866,7 +1689,7 @@
         <v>103800</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1874,34 +1697,22 @@
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
-        <v>1</v>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G5" s="1">
         <v>1131001</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1131001</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="1">
-        <v>2131001</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:16">
+        <v>28</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:12">
       <c r="A6" s="1">
         <v>100102</v>
       </c>
@@ -1909,7 +1720,7 @@
         <v>103800</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1917,34 +1728,22 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
+      <c r="F6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G6" s="1">
         <v>1131101</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1131101</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2131101</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:16">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:12">
       <c r="A7" s="1">
         <v>100103</v>
       </c>
@@ -1952,7 +1751,7 @@
         <v>103800</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1960,34 +1759,22 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1">
-        <v>3</v>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G7" s="1">
         <v>1131201</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="1">
-        <v>1131201</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="1">
-        <v>2131201</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:16">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:12">
       <c r="A8" s="1">
         <v>100104</v>
       </c>
@@ -1995,7 +1782,7 @@
         <v>103800</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -2003,34 +1790,22 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="1">
-        <v>4</v>
+      <c r="F8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G8" s="1">
         <v>1131301</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1131301</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" s="1">
-        <v>2131301</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:16">
+        <v>34</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:12">
       <c r="A9" s="1">
         <v>100105</v>
       </c>
@@ -2038,7 +1813,7 @@
         <v>103800</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -2046,34 +1821,22 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="1">
-        <v>5</v>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G9" s="1">
         <v>1131401</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1131401</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="1">
-        <v>2131401</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:16">
+        <v>36</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:12">
       <c r="A10" s="1">
         <v>100106</v>
       </c>
@@ -2081,42 +1844,30 @@
         <v>103800</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="4">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
         <v>1</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="F10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="3">
         <v>1131002</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="4">
-        <v>1131002</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="4">
-        <v>2131002</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="P10" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:16">
+      <c r="H10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:12">
       <c r="A11" s="1">
         <v>100107</v>
       </c>
@@ -2124,42 +1875,30 @@
         <v>103800</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="4">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>2</v>
       </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="F11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="3">
         <v>1131102</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="4">
-        <v>1131102</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="4">
-        <v>2131102</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="P11" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:16">
+      <c r="H11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
       <c r="A12" s="1">
         <v>100108</v>
       </c>
@@ -2167,42 +1906,30 @@
         <v>103800</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="4">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
-        <v>3</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="F12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="3">
         <v>1131202</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="4">
-        <v>1131202</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="4">
-        <v>2131202</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="P12" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:16">
+      <c r="H12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
       <c r="A13" s="1">
         <v>100109</v>
       </c>
@@ -2210,42 +1937,30 @@
         <v>103800</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="4">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="F13" s="4">
-        <v>4</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="F13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="3">
         <v>1131302</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="4">
-        <v>1131302</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" s="4">
-        <v>2131302</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="P13" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:16">
+      <c r="H13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
       <c r="A14" s="1">
         <v>100110</v>
       </c>
@@ -2253,42 +1968,30 @@
         <v>103800</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="4">
+        <v>25</v>
+      </c>
+      <c r="D14" s="3">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
-        <v>5</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="F14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="3">
         <v>1131402</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="4">
-        <v>1131402</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" s="4">
-        <v>2131402</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="P14" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:16">
+      <c r="H14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
       <c r="A15" s="1">
         <v>100201</v>
       </c>
@@ -2296,7 +1999,7 @@
         <v>103800</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -2304,33 +2007,21 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="1">
-        <v>1</v>
+      <c r="F15" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="G15" s="1">
         <v>1131004</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1131003</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2131003</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
       <c r="A16" s="1">
         <v>100202</v>
       </c>
@@ -2338,7 +2029,7 @@
         <v>103800</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -2346,33 +2037,21 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="1">
-        <v>2</v>
+      <c r="F16" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="G16" s="1">
         <v>1131104</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1131103</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2131103</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
       <c r="A17" s="1">
         <v>100203</v>
       </c>
@@ -2380,7 +2059,7 @@
         <v>103800</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -2388,33 +2067,21 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="1">
-        <v>3</v>
+      <c r="F17" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="G17" s="1">
         <v>1131204</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1131203</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K17" s="1">
-        <v>2131203</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
       <c r="A18" s="1">
         <v>100204</v>
       </c>
@@ -2422,7 +2089,7 @@
         <v>103800</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -2430,33 +2097,21 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="1">
-        <v>4</v>
+      <c r="F18" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="G18" s="1">
         <v>1131304</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1131303</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18" s="1">
-        <v>2131303</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:15">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:11">
       <c r="A19" s="1">
         <v>100205</v>
       </c>
@@ -2464,7 +2119,7 @@
         <v>103800</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -2472,33 +2127,21 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="1">
-        <v>5</v>
+      <c r="F19" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="G19" s="1">
         <v>1131404</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="1">
-        <v>1131403</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K19" s="1">
-        <v>2131403</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:15">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:11">
       <c r="A20" s="1">
         <v>100206</v>
       </c>
@@ -2506,41 +2149,29 @@
         <v>103800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="4">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3">
         <v>2</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>2</v>
       </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="F20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="3">
         <v>1131003</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" s="4">
-        <v>1131004</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K20" s="4">
-        <v>2131004</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:15">
+      <c r="H20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:11">
       <c r="A21" s="1">
         <v>100207</v>
       </c>
@@ -2548,41 +2179,29 @@
         <v>103800</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="4">
+        <v>25</v>
+      </c>
+      <c r="D21" s="3">
         <v>2</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>2</v>
       </c>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="F21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="3">
         <v>1131103</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I21" s="4">
-        <v>1131104</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="K21" s="4">
-        <v>2131104</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:15">
+      <c r="H21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
       <c r="A22" s="1">
         <v>100208</v>
       </c>
@@ -2590,41 +2209,29 @@
         <v>103800</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="4">
+        <v>25</v>
+      </c>
+      <c r="D22" s="3">
         <v>2</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>2</v>
       </c>
-      <c r="F22" s="4">
-        <v>3</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="F22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="3">
         <v>1131203</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I22" s="4">
-        <v>1131204</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K22" s="4">
-        <v>2131204</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:15">
+      <c r="H22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
       <c r="A23" s="1">
         <v>100209</v>
       </c>
@@ -2632,41 +2239,29 @@
         <v>103800</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="4">
+        <v>25</v>
+      </c>
+      <c r="D23" s="3">
         <v>2</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <v>2</v>
       </c>
-      <c r="F23" s="4">
-        <v>4</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="F23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="3">
         <v>1131303</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I23" s="4">
-        <v>1131304</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K23" s="4">
-        <v>2131304</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:15">
+      <c r="H23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
       <c r="A24" s="1">
         <v>100210</v>
       </c>
@@ -2674,41 +2269,29 @@
         <v>103800</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="4">
+        <v>25</v>
+      </c>
+      <c r="D24" s="3">
         <v>2</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <v>2</v>
       </c>
-      <c r="F24" s="4">
-        <v>5</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="F24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="3">
         <v>1131403</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I24" s="4">
-        <v>1131404</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K24" s="4">
-        <v>2131404</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:15">
+      <c r="H24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:11">
       <c r="A25" s="1">
         <v>100301</v>
       </c>
@@ -2716,7 +2299,7 @@
         <v>103800</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -2724,34 +2307,22 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="1">
-        <v>1</v>
+      <c r="F25" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G25" s="1">
-        <v>1131005</v>
+        <v>1131006</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1131005</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K25" s="1">
-        <v>2131005</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:15">
+        <v>71</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:11">
       <c r="A26" s="1">
         <v>100302</v>
       </c>
@@ -2759,7 +2330,7 @@
         <v>103800</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -2767,34 +2338,22 @@
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="1">
-        <v>2</v>
+      <c r="F26" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G26" s="1">
-        <v>1131105</v>
+        <v>1131106</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1131105</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K26" s="1">
-        <v>2131105</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:15">
+        <v>73</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:11">
       <c r="A27" s="1">
         <v>100303</v>
       </c>
@@ -2802,7 +2361,7 @@
         <v>103800</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -2810,34 +2369,22 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="1">
-        <v>3</v>
+      <c r="F27" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G27" s="1">
-        <v>1131205</v>
+        <v>1131206</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="1">
-        <v>1131205</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K27" s="1">
-        <v>2131205</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:15">
+        <v>75</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:11">
       <c r="A28" s="1">
         <v>100304</v>
       </c>
@@ -2845,7 +2392,7 @@
         <v>103800</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -2853,34 +2400,22 @@
       <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="1">
-        <v>4</v>
+      <c r="F28" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G28" s="1">
-        <v>1131305</v>
+        <v>1131306</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1131305</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="K28" s="1">
-        <v>2131305</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:15">
+        <v>77</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:11">
       <c r="A29" s="1">
         <v>100305</v>
       </c>
@@ -2888,7 +2423,7 @@
         <v>103800</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -2896,34 +2431,22 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="1">
-        <v>5</v>
+      <c r="F29" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G29" s="1">
-        <v>1131405</v>
+        <v>1131406</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1131405</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K29" s="1">
-        <v>2131405</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:15">
+        <v>79</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:11">
       <c r="A30" s="1">
         <v>100306</v>
       </c>
@@ -2931,41 +2454,29 @@
         <v>103800</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="4">
+        <v>25</v>
+      </c>
+      <c r="D30" s="3">
         <v>3</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="3">
         <v>2</v>
       </c>
-      <c r="F30" s="4">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4">
-        <v>1131006</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>112</v>
+      <c r="F30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1131005</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="I30" s="4">
-        <v>1131006</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K30" s="4">
-        <v>2131006</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="M30" s="2">
         <v>200</v>
       </c>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:15">
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:11">
       <c r="A31" s="1">
         <v>100307</v>
       </c>
@@ -2973,41 +2484,29 @@
         <v>103800</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="4">
+        <v>25</v>
+      </c>
+      <c r="D31" s="3">
         <v>3</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="3">
         <v>2</v>
       </c>
-      <c r="F31" s="4">
-        <v>2</v>
-      </c>
-      <c r="G31" s="4">
-        <v>1131106</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I31" s="4">
-        <v>1131106</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="K31" s="4">
-        <v>2131106</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="N31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:15">
+      <c r="F31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1131105</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:11">
       <c r="A32" s="1">
         <v>100308</v>
       </c>
@@ -3015,41 +2514,29 @@
         <v>103800</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="4">
+        <v>25</v>
+      </c>
+      <c r="D32" s="3">
         <v>3</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>2</v>
       </c>
-      <c r="F32" s="4">
-        <v>3</v>
-      </c>
-      <c r="G32" s="4">
-        <v>1131206</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1131206</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="K32" s="4">
-        <v>2131206</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:14">
+      <c r="F32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1131205</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:10">
       <c r="A33" s="1">
         <v>100309</v>
       </c>
@@ -3057,41 +2544,29 @@
         <v>103800</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="4">
+        <v>25</v>
+      </c>
+      <c r="D33" s="3">
         <v>3</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="3">
         <v>2</v>
       </c>
-      <c r="F33" s="4">
-        <v>4</v>
-      </c>
-      <c r="G33" s="4">
-        <v>1131306</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I33" s="4">
-        <v>1131306</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="K33" s="4">
-        <v>2131306</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="N33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:14">
+      <c r="F33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1131305</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:10">
       <c r="A34" s="1">
         <v>100310</v>
       </c>
@@ -3099,519 +2574,387 @@
         <v>103800</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" s="4">
+        <v>25</v>
+      </c>
+      <c r="D34" s="3">
         <v>3</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="3">
         <v>2</v>
       </c>
-      <c r="F34" s="4">
-        <v>5</v>
-      </c>
-      <c r="G34" s="4">
-        <v>1131406</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I34" s="4">
-        <v>1131406</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="K34" s="4">
-        <v>2131406</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:14">
+      <c r="F34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1131405</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:10">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="F35" s="5"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:14">
+    </row>
+    <row r="36" customHeight="1" spans="1:10">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+      <c r="F36" s="5"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:14">
+    </row>
+    <row r="37" customHeight="1" spans="1:10">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+      <c r="F37" s="5"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:14">
+    </row>
+    <row r="38" customHeight="1" spans="1:10">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="F38" s="5"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
+      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:14">
+    </row>
+    <row r="39" customHeight="1" spans="1:10">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
+      <c r="F39" s="5"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:14">
+    </row>
+    <row r="40" customHeight="1" spans="1:10">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="F40" s="5"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:14">
+    </row>
+    <row r="41" customHeight="1" spans="1:10">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="F41" s="5"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
+      <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:14">
+    </row>
+    <row r="42" customHeight="1" spans="1:10">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="F42" s="5"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
+      <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:14">
+    </row>
+    <row r="43" customHeight="1" spans="1:10">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="F43" s="5"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
+      <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:14">
+    </row>
+    <row r="44" customHeight="1" spans="1:10">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+      <c r="F44" s="5"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
+      <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:14">
+    </row>
+    <row r="45" customHeight="1" spans="1:10">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="F45" s="5"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
+      <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:14">
+    </row>
+    <row r="46" customHeight="1" spans="1:10">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="F46" s="5"/>
       <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
+      <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:14">
+    </row>
+    <row r="47" customHeight="1" spans="1:10">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
+      <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:14">
+    </row>
+    <row r="48" customHeight="1" spans="1:10">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="F48" s="5"/>
       <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
+      <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:14">
+    </row>
+    <row r="49" customHeight="1" spans="1:10">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
+      <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:14">
+    </row>
+    <row r="50" customHeight="1" spans="1:10">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="F50" s="5"/>
       <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
+      <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:14">
+    </row>
+    <row r="51" customHeight="1" spans="1:10">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
+      <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:14">
+    </row>
+    <row r="52" customHeight="1" spans="1:10">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="F52" s="5"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
+      <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:14">
+    </row>
+    <row r="53" customHeight="1" spans="1:10">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
+      <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:14">
+    </row>
+    <row r="54" customHeight="1" spans="1:10">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="F54" s="5"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
+      <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:14">
+    </row>
+    <row r="55" customHeight="1" spans="1:10">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
+      <c r="F55" s="5"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
+      <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:14">
+    </row>
+    <row r="56" customHeight="1" spans="1:10">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+      <c r="F56" s="5"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
+      <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:14">
+    </row>
+    <row r="57" customHeight="1" spans="1:10">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
+      <c r="F57" s="5"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
+      <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:14">
+    </row>
+    <row r="58" customHeight="1" spans="1:10">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
+      <c r="F58" s="5"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
+      <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:14">
+    </row>
+    <row r="59" customHeight="1" spans="1:10">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
+      <c r="F59" s="5"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
+      <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:14">
+    </row>
+    <row r="60" customHeight="1" spans="1:10">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
+      <c r="F60" s="5"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
+      <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:14">
+    </row>
+    <row r="61" customHeight="1" spans="1:10">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
+      <c r="F61" s="5"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
+      <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:14">
+    </row>
+    <row r="62" customHeight="1" spans="1:10">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
+      <c r="F62" s="5"/>
       <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
+      <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:14">
+    </row>
+    <row r="63" customHeight="1" spans="1:10">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
+      <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:14">
+    </row>
+    <row r="64" customHeight="1" spans="1:10">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
+      <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/SeasonGem.xlsx
+++ b/hall/resources/sample/SeasonGem.xlsx
@@ -56,7 +56,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+该数字用于仅前端显示（叠加统计），替换多语言宝石描述的数字占位符</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="93">
   <si>
     <t>ID</t>
   </si>
@@ -109,6 +131,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>属性提升</t>
+  </si>
+  <si>
     <t>金额解锁</t>
   </si>
   <si>
@@ -146,6 +171,9 @@
   </si>
   <si>
     <t>itemId</t>
+  </si>
+  <si>
+    <t>StatBoost</t>
   </si>
   <si>
     <t>bet</t>
@@ -1550,7 +1578,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -1559,14 +1587,15 @@
     <col min="5" max="5" width="6.5" customWidth="1"/>
     <col min="6" max="6" width="12.375" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="12.875" customWidth="1"/>
-    <col min="9" max="9" width="24.25" customWidth="1"/>
-    <col min="10" max="10" width="16.625" customWidth="1"/>
-    <col min="11" max="11" width="21.125" customWidth="1"/>
-    <col min="12" max="12" width="19.625" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="18.125" customWidth="1"/>
+    <col min="10" max="10" width="24.25" customWidth="1"/>
+    <col min="11" max="11" width="16.625" customWidth="1"/>
+    <col min="12" max="12" width="21.125" customWidth="1"/>
+    <col min="13" max="13" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:12">
+    <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1603,24 +1632,27 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
@@ -1633,42 +1665,48 @@
         <v>15</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:12">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:12">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:13">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1680,8 +1718,9 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:12">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:13">
       <c r="A5" s="1">
         <v>100101</v>
       </c>
@@ -1689,7 +1728,7 @@
         <v>103800</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1698,21 +1737,24 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1">
         <v>1131001</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:12">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:13">
       <c r="A6" s="1">
         <v>100102</v>
       </c>
@@ -1720,7 +1762,7 @@
         <v>103800</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1729,21 +1771,24 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1">
         <v>1131101</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:12">
+        <v>31</v>
+      </c>
+      <c r="I6" s="1">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:13">
       <c r="A7" s="1">
         <v>100103</v>
       </c>
@@ -1751,7 +1796,7 @@
         <v>103800</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1760,21 +1805,24 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1">
         <v>1131201</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:12">
+        <v>33</v>
+      </c>
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
       <c r="A8" s="1">
         <v>100104</v>
       </c>
@@ -1782,7 +1830,7 @@
         <v>103800</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1791,21 +1839,24 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1">
         <v>1131301</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:12">
+        <v>35</v>
+      </c>
+      <c r="I8" s="1">
+        <v>15</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
       <c r="A9" s="1">
         <v>100105</v>
       </c>
@@ -1813,7 +1864,7 @@
         <v>103800</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1822,21 +1873,24 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1">
         <v>1131401</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:12">
+        <v>37</v>
+      </c>
+      <c r="I9" s="1">
+        <v>20</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
       <c r="A10" s="1">
         <v>100106</v>
       </c>
@@ -1844,7 +1898,7 @@
         <v>103800</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1853,21 +1907,24 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G10" s="3">
         <v>1131002</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
       <c r="J10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:12">
+      <c r="K10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
       <c r="A11" s="1">
         <v>100107</v>
       </c>
@@ -1875,7 +1932,7 @@
         <v>103800</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -1884,21 +1941,24 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11" s="3">
         <v>1131102</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
       <c r="J11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:12">
+      <c r="K11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
       <c r="A12" s="1">
         <v>100108</v>
       </c>
@@ -1906,7 +1966,7 @@
         <v>103800</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -1915,21 +1975,24 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G12" s="3">
         <v>1131202</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:12">
+      <c r="K12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
       <c r="A13" s="1">
         <v>100109</v>
       </c>
@@ -1937,7 +2000,7 @@
         <v>103800</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -1946,21 +2009,24 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G13" s="3">
         <v>1131302</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="I13" s="1">
+        <v>4</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="L13" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:12">
+      <c r="K13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
       <c r="A14" s="1">
         <v>100110</v>
       </c>
@@ -1968,7 +2034,7 @@
         <v>103800</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -1977,21 +2043,24 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G14" s="3">
         <v>1131402</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="L14" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:12">
+      <c r="K14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
       <c r="A15" s="1">
         <v>100201</v>
       </c>
@@ -1999,7 +2068,7 @@
         <v>103800</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -2008,20 +2077,23 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G15" s="1">
         <v>1131004</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:12">
+        <v>51</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
       <c r="A16" s="1">
         <v>100202</v>
       </c>
@@ -2029,7 +2101,7 @@
         <v>103800</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -2038,20 +2110,23 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G16" s="1">
         <v>1131104</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
+        <v>53</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:12">
       <c r="A17" s="1">
         <v>100203</v>
       </c>
@@ -2059,7 +2134,7 @@
         <v>103800</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -2068,20 +2143,23 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G17" s="1">
         <v>1131204</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
+        <v>55</v>
+      </c>
+      <c r="I17" s="1">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
       <c r="A18" s="1">
         <v>100204</v>
       </c>
@@ -2089,7 +2167,7 @@
         <v>103800</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -2098,20 +2176,23 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G18" s="1">
         <v>1131304</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:12">
       <c r="A19" s="1">
         <v>100205</v>
       </c>
@@ -2119,7 +2200,7 @@
         <v>103800</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -2128,20 +2209,23 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" s="1">
         <v>1131404</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:11">
+        <v>59</v>
+      </c>
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:12">
       <c r="A20" s="1">
         <v>100206</v>
       </c>
@@ -2149,7 +2233,7 @@
         <v>103800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3">
         <v>2</v>
@@ -2158,20 +2242,23 @@
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G20" s="3">
         <v>1131003</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:11">
+        <v>62</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:12">
       <c r="A21" s="1">
         <v>100207</v>
       </c>
@@ -2179,7 +2266,7 @@
         <v>103800</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D21" s="3">
         <v>2</v>
@@ -2188,20 +2275,23 @@
         <v>2</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G21" s="3">
         <v>1131103</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
+        <v>64</v>
+      </c>
+      <c r="I21" s="1">
+        <v>4</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:12">
       <c r="A22" s="1">
         <v>100208</v>
       </c>
@@ -2209,7 +2299,7 @@
         <v>103800</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D22" s="3">
         <v>2</v>
@@ -2218,20 +2308,23 @@
         <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G22" s="3">
         <v>1131203</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
+        <v>66</v>
+      </c>
+      <c r="I22" s="1">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
       <c r="A23" s="1">
         <v>100209</v>
       </c>
@@ -2239,7 +2332,7 @@
         <v>103800</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D23" s="3">
         <v>2</v>
@@ -2248,20 +2341,23 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G23" s="3">
         <v>1131303</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
+        <v>68</v>
+      </c>
+      <c r="I23" s="1">
+        <v>8</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:12">
       <c r="A24" s="1">
         <v>100210</v>
       </c>
@@ -2269,7 +2365,7 @@
         <v>103800</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -2278,20 +2374,23 @@
         <v>2</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G24" s="3">
         <v>1131403</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:11">
+        <v>70</v>
+      </c>
+      <c r="I24" s="1">
+        <v>10</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:12">
       <c r="A25" s="1">
         <v>100301</v>
       </c>
@@ -2299,7 +2398,7 @@
         <v>103800</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -2308,21 +2407,24 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G25" s="1">
         <v>1131006</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:11">
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
       <c r="A26" s="1">
         <v>100302</v>
       </c>
@@ -2330,7 +2432,7 @@
         <v>103800</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -2339,21 +2441,24 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G26" s="1">
         <v>1131106</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I26" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="I26" s="1">
+        <v>4</v>
+      </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:11">
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
       <c r="A27" s="1">
         <v>100303</v>
       </c>
@@ -2361,7 +2466,7 @@
         <v>103800</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -2370,21 +2475,24 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G27" s="1">
         <v>1131206</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I27" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="I27" s="1">
+        <v>6</v>
+      </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:11">
+      <c r="K27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
       <c r="A28" s="1">
         <v>100304</v>
       </c>
@@ -2392,7 +2500,7 @@
         <v>103800</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -2401,21 +2509,24 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G28" s="1">
         <v>1131306</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I28" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="I28" s="1">
+        <v>8</v>
+      </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:11">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:12">
       <c r="A29" s="1">
         <v>100305</v>
       </c>
@@ -2423,7 +2534,7 @@
         <v>103800</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -2432,21 +2543,24 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G29" s="1">
         <v>1131406</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I29" s="1"/>
+        <v>81</v>
+      </c>
+      <c r="I29" s="1">
+        <v>10</v>
+      </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:11">
+      <c r="K29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
       <c r="A30" s="1">
         <v>100306</v>
       </c>
@@ -2454,7 +2568,7 @@
         <v>103800</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D30" s="3">
         <v>3</v>
@@ -2463,20 +2577,23 @@
         <v>2</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G30" s="3">
         <v>1131005</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I30" s="4">
         <v>200</v>
       </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:11">
+      <c r="J30" s="4">
+        <v>200</v>
+      </c>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
       <c r="A31" s="1">
         <v>100307</v>
       </c>
@@ -2484,7 +2601,7 @@
         <v>103800</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D31" s="3">
         <v>3</v>
@@ -2493,20 +2610,23 @@
         <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G31" s="3">
         <v>1131105</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="I31" s="4">
+        <v>400</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:12">
       <c r="A32" s="1">
         <v>100308</v>
       </c>
@@ -2514,7 +2634,7 @@
         <v>103800</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>3</v>
@@ -2523,20 +2643,23 @@
         <v>2</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G32" s="3">
         <v>1131205</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:10">
+        <v>87</v>
+      </c>
+      <c r="I32" s="4">
+        <v>600</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:11">
       <c r="A33" s="1">
         <v>100309</v>
       </c>
@@ -2544,7 +2667,7 @@
         <v>103800</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D33" s="3">
         <v>3</v>
@@ -2553,20 +2676,23 @@
         <v>2</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G33" s="3">
         <v>1131305</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:10">
+        <v>89</v>
+      </c>
+      <c r="I33" s="4">
+        <v>800</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:11">
       <c r="A34" s="1">
         <v>100310</v>
       </c>
@@ -2574,7 +2700,7 @@
         <v>103800</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D34" s="3">
         <v>3</v>
@@ -2583,20 +2709,23 @@
         <v>2</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G34" s="3">
         <v>1131405</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:10">
+        <v>91</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:11">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2607,8 +2736,9 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:10">
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:11">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2619,8 +2749,9 @@
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:10">
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:11">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2631,8 +2762,9 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:10">
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:11">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2643,8 +2775,9 @@
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:10">
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:11">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2655,8 +2788,9 @@
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:10">
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:11">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2667,8 +2801,9 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:10">
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:11">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2679,8 +2814,9 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:10">
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:11">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2691,8 +2827,9 @@
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:10">
+      <c r="K42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:11">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2703,8 +2840,9 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:10">
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:11">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2715,8 +2853,9 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:10">
+      <c r="K44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:11">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2727,8 +2866,9 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:10">
+      <c r="K45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:11">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2739,8 +2879,9 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:10">
+      <c r="K46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:11">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2751,8 +2892,9 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:10">
+      <c r="K47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2763,8 +2905,9 @@
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:10">
+      <c r="K48" s="1"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:11">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2775,8 +2918,9 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:10">
+      <c r="K49" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:11">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2787,8 +2931,9 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:10">
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2799,8 +2944,9 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:10">
+      <c r="K51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2811,8 +2957,9 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:10">
+      <c r="K52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:11">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2823,8 +2970,9 @@
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:10">
+      <c r="K53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:11">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2835,8 +2983,9 @@
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:10">
+      <c r="K54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:11">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2847,8 +2996,9 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:10">
+      <c r="K55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:11">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2859,8 +3009,9 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:10">
+      <c r="K56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:11">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2871,8 +3022,9 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:10">
+      <c r="K57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:11">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2883,8 +3035,9 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:10">
+      <c r="K58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:11">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2895,8 +3048,9 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:10">
+      <c r="K59" s="1"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:11">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2907,8 +3061,9 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:10">
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:11">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2919,8 +3074,9 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:10">
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:11">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2931,8 +3087,9 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:10">
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:11">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2943,8 +3100,9 @@
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:10">
+      <c r="K63" s="1"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:11">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2955,6 +3113,7 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/SeasonGem.xlsx
+++ b/hall/resources/sample/SeasonGem.xlsx
@@ -365,25 +365,25 @@
     <t>下注提升.绿</t>
   </si>
   <si>
-    <t>200_400</t>
+    <t>400_800</t>
   </si>
   <si>
     <t>下注提升.蓝</t>
   </si>
   <si>
-    <t>200_400_600</t>
+    <t>400_800_1000</t>
   </si>
   <si>
     <t>下注提升.紫</t>
   </si>
   <si>
-    <t>200_400_600_800</t>
+    <t>400_800_1000_1200</t>
   </si>
   <si>
     <t>下注提升.橙</t>
   </si>
   <si>
-    <t>200_400_600_800_1000</t>
+    <t>400_800_1000_1200_2000</t>
   </si>
 </sst>
 </file>
@@ -2586,10 +2586,10 @@
         <v>84</v>
       </c>
       <c r="I30" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J30" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K30" s="1"/>
     </row>
@@ -2619,7 +2619,7 @@
         <v>85</v>
       </c>
       <c r="I31" s="4">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>86</v>
@@ -2652,7 +2652,7 @@
         <v>87</v>
       </c>
       <c r="I32" s="4">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>88</v>
@@ -2685,7 +2685,7 @@
         <v>89</v>
       </c>
       <c r="I33" s="4">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>90</v>
@@ -2718,7 +2718,7 @@
         <v>91</v>
       </c>
       <c r="I34" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>92</v>

--- a/hall/resources/sample/SeasonGem.xlsx
+++ b/hall/resources/sample/SeasonGem.xlsx
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
@@ -149,7 +149,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>list&lt;long&gt;{_}</t>
+    <t>map&lt;int{,}list&lt;long&gt;{_}&gt;{|}</t>
   </si>
   <si>
     <t>map&lt;int{,}map&lt;int{_}int&gt;{|}&gt;{;}</t>
@@ -362,28 +362,31 @@
     <t>下注提升.白</t>
   </si>
   <si>
+    <t>1,400|2,400_800|3,400_800_1200</t>
+  </si>
+  <si>
     <t>下注提升.绿</t>
   </si>
   <si>
-    <t>400_800</t>
+    <t>1,400_600|2,400_600_1200|3,400_600_1200_1800</t>
   </si>
   <si>
     <t>下注提升.蓝</t>
   </si>
   <si>
-    <t>400_800_1000</t>
+    <t>1,400_600_800|2,400_600_800_1600|3,400_600_800_1600_2400</t>
   </si>
   <si>
     <t>下注提升.紫</t>
   </si>
   <si>
-    <t>400_800_1000_1200</t>
+    <t>1,400_600_800_1000|2,400_600_800_1000_2000|2,400_600_800_1000_2000_3000</t>
   </si>
   <si>
     <t>下注提升.橙</t>
   </si>
   <si>
-    <t>400_800_1000_1200_2000</t>
+    <t>1,400_600_800_1000_1200|2,400_600_800_1000_1200_2400|3,400_600_800_1000_1200_2400_3600</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1037,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1048,6 +1051,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1589,7 +1595,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
     <col min="9" max="9" width="18.125" customWidth="1"/>
-    <col min="10" max="10" width="24.25" customWidth="1"/>
+    <col min="10" max="10" width="25.875" customWidth="1"/>
     <col min="11" max="11" width="16.625" customWidth="1"/>
     <col min="12" max="12" width="21.125" customWidth="1"/>
     <col min="13" max="13" width="19.625" customWidth="1"/>
@@ -2588,8 +2594,8 @@
       <c r="I30" s="4">
         <v>400</v>
       </c>
-      <c r="J30" s="4">
-        <v>400</v>
+      <c r="J30" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="K30" s="1"/>
     </row>
@@ -2616,13 +2622,13 @@
         <v>1131105</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I31" s="4">
-        <v>800</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>86</v>
+        <v>600</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="K31" s="1"/>
     </row>
@@ -2649,13 +2655,13 @@
         <v>1131205</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I32" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>88</v>
+        <v>800</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="K32" s="1"/>
     </row>
@@ -2682,13 +2688,13 @@
         <v>1131305</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I33" s="4">
-        <v>1200</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>90</v>
+        <v>1000</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K33" s="1"/>
     </row>
@@ -2715,13 +2721,13 @@
         <v>1131405</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I34" s="4">
-        <v>2000</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>92</v>
+        <v>1200</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="K34" s="1"/>
     </row>
@@ -2731,8 +2737,8 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -2744,8 +2750,8 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -2757,8 +2763,8 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -2770,8 +2776,8 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -2783,8 +2789,8 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -2796,8 +2802,8 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -2809,8 +2815,8 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -2822,8 +2828,8 @@
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -2835,8 +2841,8 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -2848,8 +2854,8 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2861,8 +2867,8 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2874,8 +2880,8 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2887,8 +2893,8 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2900,8 +2906,8 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -2913,8 +2919,8 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2926,8 +2932,8 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -2939,8 +2945,8 @@
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2952,8 +2958,8 @@
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2965,8 +2971,8 @@
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2978,8 +2984,8 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2991,8 +2997,8 @@
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -3004,8 +3010,8 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3017,8 +3023,8 @@
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -3030,8 +3036,8 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -3043,8 +3049,8 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -3056,8 +3062,8 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -3069,8 +3075,8 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -3082,8 +3088,8 @@
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -3095,8 +3101,8 @@
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -3108,8 +3114,8 @@
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>

--- a/hall/resources/sample/SeasonGem.xlsx
+++ b/hall/resources/sample/SeasonGem.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -100,12 +100,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="I35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+每分钟获取数量</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="102">
   <si>
     <t>ID</t>
   </si>
@@ -146,6 +168,9 @@
     <t>特殊模式中奖概率提升</t>
   </si>
   <si>
+    <t>每天获取收益的时间上限（min）</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -188,6 +213,9 @@
     <t>specialModeProbUp</t>
   </si>
   <si>
+    <t>MaxEarningTime</t>
+  </si>
+  <si>
     <t>恶魔之子</t>
   </si>
   <si>
@@ -387,6 +415,24 @@
   </si>
   <si>
     <t>1,400_600_800_1000_1200|2,400_600_800_1000_1200_2400|3,400_600_800_1000_1200_2400_3600</t>
+  </si>
+  <si>
+    <t>挂机收益</t>
+  </si>
+  <si>
+    <t>挂机收益.白</t>
+  </si>
+  <si>
+    <t>挂机收益.绿</t>
+  </si>
+  <si>
+    <t>挂机收益.蓝</t>
+  </si>
+  <si>
+    <t>挂机收益.紫</t>
+  </si>
+  <si>
+    <t>挂机收益.橙</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1057,6 +1103,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1584,7 +1633,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -1599,9 +1648,10 @@
     <col min="11" max="11" width="16.625" customWidth="1"/>
     <col min="12" max="12" width="21.125" customWidth="1"/>
     <col min="13" max="13" width="19.625" customWidth="1"/>
+    <col min="14" max="14" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:13">
+    <row r="1" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1641,78 +1691,87 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:13">
+    </row>
+    <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:13">
+        <v>27</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:14">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1726,7 +1785,7 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" customHeight="1" spans="1:13">
+    <row r="5" customHeight="1" spans="1:14">
       <c r="A5" s="1">
         <v>100101</v>
       </c>
@@ -1734,7 +1793,7 @@
         <v>103800</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1743,24 +1802,24 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>1131001</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" customHeight="1" spans="1:13">
+    <row r="6" customHeight="1" spans="1:14">
       <c r="A6" s="1">
         <v>100102</v>
       </c>
@@ -1768,7 +1827,7 @@
         <v>103800</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1777,24 +1836,24 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6" s="1">
         <v>1131101</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" customHeight="1" spans="1:13">
+    <row r="7" customHeight="1" spans="1:14">
       <c r="A7" s="1">
         <v>100103</v>
       </c>
@@ -1802,7 +1861,7 @@
         <v>103800</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1811,24 +1870,24 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
         <v>1131201</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1">
         <v>10</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" customHeight="1" spans="1:13">
+    <row r="8" customHeight="1" spans="1:14">
       <c r="A8" s="1">
         <v>100104</v>
       </c>
@@ -1836,7 +1895,7 @@
         <v>103800</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1845,24 +1904,24 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <v>1131301</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8" s="1">
         <v>15</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" customHeight="1" spans="1:13">
+    <row r="9" customHeight="1" spans="1:14">
       <c r="A9" s="1">
         <v>100105</v>
       </c>
@@ -1870,7 +1929,7 @@
         <v>103800</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1879,24 +1938,24 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>1131401</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I9" s="1">
         <v>20</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" customHeight="1" spans="1:13">
+    <row r="10" customHeight="1" spans="1:14">
       <c r="A10" s="1">
         <v>100106</v>
       </c>
@@ -1904,7 +1963,7 @@
         <v>103800</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1913,13 +1972,13 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G10" s="3">
         <v>1131002</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -1927,10 +1986,10 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:14">
       <c r="A11" s="1">
         <v>100107</v>
       </c>
@@ -1938,7 +1997,7 @@
         <v>103800</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -1947,13 +2006,13 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G11" s="3">
         <v>1131102</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
@@ -1961,10 +2020,10 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:14">
       <c r="A12" s="1">
         <v>100108</v>
       </c>
@@ -1972,7 +2031,7 @@
         <v>103800</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -1981,13 +2040,13 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12" s="3">
         <v>1131202</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I12" s="1">
         <v>3</v>
@@ -1995,10 +2054,10 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:13">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:14">
       <c r="A13" s="1">
         <v>100109</v>
       </c>
@@ -2006,7 +2065,7 @@
         <v>103800</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -2015,13 +2074,13 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3">
         <v>1131302</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I13" s="1">
         <v>4</v>
@@ -2029,10 +2088,10 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:13">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:14">
       <c r="A14" s="1">
         <v>100110</v>
       </c>
@@ -2040,7 +2099,7 @@
         <v>103800</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -2049,13 +2108,13 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3">
         <v>1131402</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I14" s="1">
         <v>5</v>
@@ -2063,10 +2122,10 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="1">
         <v>100201</v>
       </c>
@@ -2074,7 +2133,7 @@
         <v>103800</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -2083,23 +2142,23 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G15" s="1">
         <v>1131004</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I15" s="1">
         <v>2</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:13">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1">
         <v>100202</v>
       </c>
@@ -2107,7 +2166,7 @@
         <v>103800</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -2116,20 +2175,20 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G16" s="1">
         <v>1131104</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I16" s="1">
         <v>4</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:12">
@@ -2140,7 +2199,7 @@
         <v>103800</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -2149,20 +2208,20 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G17" s="1">
         <v>1131204</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I17" s="1">
         <v>6</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:12">
@@ -2173,7 +2232,7 @@
         <v>103800</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -2182,20 +2241,20 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G18" s="1">
         <v>1131304</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I18" s="1">
         <v>8</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:12">
@@ -2206,7 +2265,7 @@
         <v>103800</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -2215,20 +2274,20 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G19" s="1">
         <v>1131404</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I19" s="1">
         <v>10</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:12">
@@ -2239,7 +2298,7 @@
         <v>103800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3">
         <v>2</v>
@@ -2248,20 +2307,20 @@
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G20" s="3">
         <v>1131003</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I20" s="1">
         <v>2</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:12">
@@ -2272,7 +2331,7 @@
         <v>103800</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21" s="3">
         <v>2</v>
@@ -2281,20 +2340,20 @@
         <v>2</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G21" s="3">
         <v>1131103</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I21" s="1">
         <v>4</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:12">
@@ -2305,7 +2364,7 @@
         <v>103800</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="3">
         <v>2</v>
@@ -2314,20 +2373,20 @@
         <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G22" s="3">
         <v>1131203</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I22" s="1">
         <v>6</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:12">
@@ -2338,7 +2397,7 @@
         <v>103800</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D23" s="3">
         <v>2</v>
@@ -2347,20 +2406,20 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G23" s="3">
         <v>1131303</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I23" s="1">
         <v>8</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:12">
@@ -2371,7 +2430,7 @@
         <v>103800</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -2380,20 +2439,20 @@
         <v>2</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G24" s="3">
         <v>1131403</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I24" s="1">
         <v>10</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:12">
@@ -2404,7 +2463,7 @@
         <v>103800</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -2413,13 +2472,13 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G25" s="1">
         <v>1131006</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I25" s="1">
         <v>2</v>
@@ -2427,7 +2486,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:12">
@@ -2438,7 +2497,7 @@
         <v>103800</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -2447,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G26" s="1">
         <v>1131106</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I26" s="1">
         <v>4</v>
@@ -2461,7 +2520,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:12">
@@ -2472,7 +2531,7 @@
         <v>103800</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -2481,13 +2540,13 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G27" s="1">
         <v>1131206</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I27" s="1">
         <v>6</v>
@@ -2495,7 +2554,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:12">
@@ -2506,7 +2565,7 @@
         <v>103800</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -2515,13 +2574,13 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G28" s="1">
         <v>1131306</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I28" s="1">
         <v>8</v>
@@ -2529,7 +2588,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:12">
@@ -2540,7 +2599,7 @@
         <v>103800</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -2549,13 +2608,13 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G29" s="1">
         <v>1131406</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I29" s="1">
         <v>10</v>
@@ -2563,7 +2622,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:12">
@@ -2574,7 +2633,7 @@
         <v>103800</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D30" s="3">
         <v>3</v>
@@ -2583,19 +2642,19 @@
         <v>2</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G30" s="3">
         <v>1131005</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I30" s="4">
         <v>400</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K30" s="1"/>
     </row>
@@ -2607,7 +2666,7 @@
         <v>103800</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D31" s="3">
         <v>3</v>
@@ -2616,19 +2675,19 @@
         <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G31" s="3">
         <v>1131105</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I31" s="4">
         <v>600</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K31" s="1"/>
     </row>
@@ -2640,7 +2699,7 @@
         <v>103800</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D32" s="3">
         <v>3</v>
@@ -2649,23 +2708,23 @@
         <v>2</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G32" s="3">
         <v>1131205</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I32" s="4">
         <v>800</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" customHeight="1" spans="1:11">
+    <row r="33" customHeight="1" spans="1:14">
       <c r="A33" s="1">
         <v>100309</v>
       </c>
@@ -2673,7 +2732,7 @@
         <v>103800</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D33" s="3">
         <v>3</v>
@@ -2682,23 +2741,23 @@
         <v>2</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G33" s="3">
         <v>1131305</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I33" s="4">
         <v>1000</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" customHeight="1" spans="1:11">
+    <row r="34" customHeight="1" spans="1:14">
       <c r="A34" s="1">
         <v>100310</v>
       </c>
@@ -2706,7 +2765,7 @@
         <v>103800</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D34" s="3">
         <v>3</v>
@@ -2715,88 +2774,183 @@
         <v>2</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G34" s="3">
         <v>1131405</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I34" s="4">
         <v>1200</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" customHeight="1" spans="1:11">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="6"/>
+    <row r="35" customHeight="1" spans="1:14">
+      <c r="A35" s="1">
+        <v>100311</v>
+      </c>
+      <c r="B35" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="G35" s="6"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="H35" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="1">
+        <v>10</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:11">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="6"/>
+      <c r="N35" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:14">
+      <c r="A36" s="1">
+        <v>100312</v>
+      </c>
+      <c r="B36" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="G36" s="6"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="H36" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="1">
+        <v>12</v>
+      </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:11">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="6"/>
+      <c r="N36" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:14">
+      <c r="A37" s="1">
+        <v>100313</v>
+      </c>
+      <c r="B37" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="G37" s="6"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="H37" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I37" s="1">
+        <v>14</v>
+      </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:11">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="6"/>
+      <c r="N37" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:14">
+      <c r="A38" s="1">
+        <v>100314</v>
+      </c>
+      <c r="B38" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="G38" s="6"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="H38" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="1">
+        <v>16</v>
+      </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:11">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="6"/>
+      <c r="N38" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:14">
+      <c r="A39" s="1">
+        <v>100315</v>
+      </c>
+      <c r="B39" s="1">
+        <v>103800</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="G39" s="6"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+      <c r="H39" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I39" s="1">
+        <v>20</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:11">
+      <c r="N39" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:14">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2809,7 +2963,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="1:11">
+    <row r="41" customHeight="1" spans="1:14">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2822,7 +2976,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" customHeight="1" spans="1:11">
+    <row r="42" customHeight="1" spans="1:14">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2835,7 +2989,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" customHeight="1" spans="1:11">
+    <row r="43" customHeight="1" spans="1:14">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2848,7 +3002,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" customHeight="1" spans="1:11">
+    <row r="44" customHeight="1" spans="1:14">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2861,7 +3015,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="1:11">
+    <row r="45" customHeight="1" spans="1:14">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2874,7 +3028,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" customHeight="1" spans="1:11">
+    <row r="46" customHeight="1" spans="1:14">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2887,7 +3041,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" customHeight="1" spans="1:11">
+    <row r="47" customHeight="1" spans="1:14">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2900,7 +3054,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
     </row>
-    <row r="48" customHeight="1" spans="1:11">
+    <row r="48" customHeight="1" spans="1:14">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>

--- a/hall/resources/sample/SeasonGem.xlsx
+++ b/hall/resources/sample/SeasonGem.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -1083,7 +1088,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1103,9 +1108,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2809,8 +2811,10 @@
       <c r="F35" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="7" t="s">
+      <c r="G35" s="1">
+        <v>1131007</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>97</v>
       </c>
       <c r="I35" s="1">
@@ -2841,8 +2845,10 @@
       <c r="F36" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="7" t="s">
+      <c r="G36" s="1">
+        <v>1131107</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>98</v>
       </c>
       <c r="I36" s="1">
@@ -2873,8 +2879,10 @@
       <c r="F37" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="7" t="s">
+      <c r="G37" s="1">
+        <v>1131207</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>99</v>
       </c>
       <c r="I37" s="1">
@@ -2905,8 +2913,10 @@
       <c r="F38" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="7" t="s">
+      <c r="G38" s="1">
+        <v>1131307</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>100</v>
       </c>
       <c r="I38" s="1">
@@ -2937,8 +2947,10 @@
       <c r="F39" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="7" t="s">
+      <c r="G39" s="1">
+        <v>1131407</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>101</v>
       </c>
       <c r="I39" s="1">
